--- a/event_registration_forms/028_virtual_family_event_attendance_form--event_registration_forms.xlsx
+++ b/event_registration_forms/028_virtual_family_event_attendance_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>event_status_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Event Status</t>
+          <t>Event Status 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>event_notes</t>
+          <t>event_notes_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Event Notes</t>
+          <t>Event Notes 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>attendee_comments</t>
+          <t>attendee_comments_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Attendee Comments</t>
+          <t>Attendee Comments 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_status_choices</t>
+          <t>event_status_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1316,7 +1316,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>event_status_choices</t>
+          <t>event_status_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>event_status_choices</t>
+          <t>event_status_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
